--- a/paper-data/2026-10-16/journal.xlsx
+++ b/paper-data/2026-10-16/journal.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,1902 @@
         <is>
           <t>slippage_bps</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:35:06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>366.3417</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9553</v>
+      </c>
+      <c r="H2" t="n">
+        <v>349.97</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>gap fade: gap +1.82% (open 369.04 vs prev close 362.44), first 5m bar red; target prev close | ctx: context filter not used by this rule (matches backtest)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>371.1018</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>362.44</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>366.5249938964844</v>
+      </c>
+      <c r="V2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:36:06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>239.7001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.4601</v>
+      </c>
+      <c r="H3" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NR7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NR7/inside breakout short through prior low 239.82 flags=['NR7'] EXPERIMENTAL | ctx: context filter not used by this rule (matches backtest)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>242.4803</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>234.1397</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>239.8200073242188</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16 08:36:06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>242.6016</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.4601</v>
+      </c>
+      <c r="H4" t="n">
+        <v>354.22</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NR7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NR7/inside breakout short through prior low 239.82 flags=['NR7'] EXPERIMENTAL</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>08:36:06</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>239.7001</v>
+      </c>
+      <c r="P4" t="n">
+        <v>242.4803</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>234.1397</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>242.4803113577707</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:12:06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>UAL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>101.6808</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.4421</v>
+      </c>
+      <c r="H5" t="n">
+        <v>350</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NR7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NR7/inside breakout long through prior high 101.63 flags=['inside_day'] EXPERIMENTAL | ctx: context filter not used by this rule (matches backtest)</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>100.7492</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>103.544</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>101.629997253418</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:53:06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>362.6212</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9553</v>
+      </c>
+      <c r="H6" t="n">
+        <v>346.41</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>gap fade: gap +1.82% (open 369.04 vs prev close 362.44), first 5m bar red; target prev close</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.016</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>08:35:06</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>366.3417</v>
+      </c>
+      <c r="P6" t="n">
+        <v>371.1018</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>362.44</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="S6" t="n">
+        <v>78</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>362.4400024414062</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:20:06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>216.4117</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.6172</v>
+      </c>
+      <c r="H7" t="n">
+        <v>349.98</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x43.8, close in bottom of range, SPY chg -0.28% | ctx: v2 px 216.52 vwap 217.13 ema20 217.16; SPY chg -0.28%; SMH chg -1.91%; tod rvol 43.82</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>216.7364</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>215.7625</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>216.5200042724609</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:22:07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>216.8447</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.6172</v>
+      </c>
+      <c r="H8" t="n">
+        <v>350.68</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x43.8, close in bottom of range, SPY chg -0.28%</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>10:20:06</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>216.4117</v>
+      </c>
+      <c r="P8" t="n">
+        <v>216.7364</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>215.7625</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>216.7363618867302</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:30:06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>530.2097</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6601</v>
+      </c>
+      <c r="H9" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x53.3, close in bottom of range, SPY chg -0.39% | ctx: v2 px 530.47 vwap 533.86 ema20 534.61; SPY chg -0.39%; XLK chg -1.96%; tod rvol 53.35</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>531.0051</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>528.6191</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>530.4749755859375</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:35:06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>225.952</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.3251</v>
+      </c>
+      <c r="H10" t="n">
+        <v>299.41</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x3.3, close in bottom of range, SPY chg -0.33% | ctx: v2 px 226.07 vwap 234.17 ema20 231.70; SPY chg -0.33%; XLK chg -1.82%; tod rvol 3.26</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>226.395</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>225.0659</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>226.0650024414062</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:36:06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>UAL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>100.6988</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.4421</v>
+      </c>
+      <c r="H11" t="n">
+        <v>346.62</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NR7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NR7/inside breakout long through prior high 101.63 flags=['inside_day'] EXPERIMENTAL</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>-3.38</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.966</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>09:12:06</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>101.6808</v>
+      </c>
+      <c r="P11" t="n">
+        <v>100.7492</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>103.544</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="S11" t="n">
+        <v>83</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
+        <v>100.7492047331674</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:36:06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>226.5082</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.3251</v>
+      </c>
+      <c r="H12" t="n">
+        <v>300.15</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x3.3, close in bottom of range, SPY chg -0.33%</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.246</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>10:35:06</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>225.952</v>
+      </c>
+      <c r="P12" t="n">
+        <v>226.395</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>225.0659</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>226.3949966430664</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:37:06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>531.2705999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6601</v>
+      </c>
+      <c r="H13" t="n">
+        <v>350.69</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x53.3, close in bottom of range, SPY chg -0.39%</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>10:30:06</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>530.2097</v>
+      </c>
+      <c r="P13" t="n">
+        <v>531.0051</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>528.6191</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="U13" t="n">
+        <v>531.0050527052919</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:55:07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>342.0889</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.0231</v>
+      </c>
+      <c r="H14" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x3.1, close in bottom of range, SPY chg -0.47% | ctx: v2 px 342.26 vwap 355.13 ema20 348.77; SPY chg -0.47%; XLK chg -1.99%; tod rvol 3.10</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>342.8649</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>340.5369</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>342.260009765625</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:55:07</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>139.0554</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.5169</v>
+      </c>
+      <c r="H15" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x4.2, close in bottom of range, SPY chg -0.47% | ctx: v2 px 139.12 vwap 144.13 ema20 142.68; SPY chg -0.47%; QQQ chg -1.48%; tod rvol 4.23</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>139.698</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>137.7703</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>139.125</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:00:07</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>175.1724</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.6818</v>
+      </c>
+      <c r="H16" t="n">
+        <v>294.6</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x3.4, close in bottom of range, SPY chg -0.55% | ctx: v2 px 175.26 vwap 177.55 ema20 176.50; SPY chg -0.55%; XLK chg -2.07%; tod rvol 3.42</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>175.615</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>174.2871</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>175.2599945068359</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:03:06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>137.8392</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.5169</v>
+      </c>
+      <c r="H17" t="n">
+        <v>346.93</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x4.2, close in bottom of range, SPY chg -0.47%</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>10:55:07</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>139.0554</v>
+      </c>
+      <c r="P17" t="n">
+        <v>139.698</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>137.7703</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S17" t="n">
+        <v>8</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>137.770301147461</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:03:06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>174.3742</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.6818</v>
+      </c>
+      <c r="H18" t="n">
+        <v>293.26</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x3.4, close in bottom of range, SPY chg -0.55%</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>11:00:07</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>175.1724</v>
+      </c>
+      <c r="P18" t="n">
+        <v>175.615</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>174.2871</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="U18" t="n">
+        <v>174.2870825424195</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:08:06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>343.0363</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.0231</v>
+      </c>
+      <c r="H19" t="n">
+        <v>350.96</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x3.1, close in bottom of range, SPY chg -0.47%</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.277</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>10:55:07</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>342.0889</v>
+      </c>
+      <c r="P19" t="n">
+        <v>342.8649</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>340.5369</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
+        <v>342.8648529052734</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:50:24</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>UAL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>98.5307</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.5521</v>
+      </c>
+      <c r="H20" t="n">
+        <v>349.99</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x3.6, close in bottom of range, SPY chg -0.74% | ctx: v2 px 98.58 vwap 100.94 ema20 99.73; SPY chg -0.74%; XLI chg -0.05%; tod rvol 3.61</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>98.785</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>98.02209999999999</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="U20" t="n">
+        <v>98.58000183105469</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:04:24</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>UAL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>98.0711</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.5521</v>
+      </c>
+      <c r="H21" t="n">
+        <v>348.36</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x3.6, close in bottom of range, SPY chg -0.74%</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>11:50:24</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>98.5307</v>
+      </c>
+      <c r="P21" t="n">
+        <v>98.785</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>98.02209999999999</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S21" t="n">
+        <v>14</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
+        <v>98.02213579559329</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:05:24</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>351.9839</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9943</v>
+      </c>
+      <c r="H22" t="n">
+        <v>349.98</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x3.9, close in bottom of range, SPY chg -0.93% | ctx: v2 px 352.16 vwap 361.04 ema20 357.31; SPY chg -0.93%; XLY chg -0.84%; tod rvol 3.86</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>353.4594</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>349.0331</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="U22" t="n">
+        <v>352.1600036621094</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:20:24</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>534.2877</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="H23" t="n">
+        <v>349.96</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x3.4, close in bottom of range, SPY chg -1.16% | ctx: v2 px 534.55 vwap 545.47 ema20 540.95; SPY chg -1.16%; SMH chg -2.56%; tod rvol 3.40</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>536.2188</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>530.4256</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>534.5549926757812</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:29:24</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>536.4869</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="H24" t="n">
+        <v>351.4</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x3.4, close in bottom of range, SPY chg -1.16%</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.412</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>12:20:24</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>534.2877</v>
+      </c>
+      <c r="P24" t="n">
+        <v>536.2188</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>530.4256</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="S24" t="n">
+        <v>9</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>536.21875</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:31:24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>353.6361</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.9943</v>
+      </c>
+      <c r="H25" t="n">
+        <v>351.62</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>RVOL spike short EXPERIMENTAL: 5m vol x3.9, close in bottom of range, SPY chg -0.93%</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.64</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.469</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>12:05:24</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>351.9839</v>
+      </c>
+      <c r="P25" t="n">
+        <v>353.4594</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>349.0331</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="S25" t="n">
+        <v>26</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>353.4593505859375</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -834,13 +2730,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3.55</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="8">
@@ -884,7 +2786,7 @@
         </is>
       </c>
       <c r="C9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -892,13 +2794,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.333</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0.15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="10">
@@ -921,13 +2829,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-7.62</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.05</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +2855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -973,6 +2887,38 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>why</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:32</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>T1: 9 trades, win rate 33% &lt; 35% and P&amp;L $-0.15 &lt; 0</t>
         </is>
       </c>
     </row>
@@ -987,7 +2933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,25 +2976,150 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1000.8</v>
+        <v>999.52</v>
       </c>
       <c r="C2" t="n">
-        <v>1000.8</v>
+        <v>296.6</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-4.24</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>996.65</v>
+      </c>
+      <c r="C3" t="n">
+        <v>299.43</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>998.03</v>
+      </c>
+      <c r="C4" t="n">
+        <v>998.03</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>996.58</v>
+      </c>
+      <c r="C5" t="n">
+        <v>996.58</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>996.58</v>
+      </c>
+      <c r="C6" t="n">
+        <v>996.58</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>996.58</v>
+      </c>
+      <c r="C7" t="n">
+        <v>996.58</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1098,7 +3169,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-16 15:00:12</t>
+          <t>2026-10-16 15:00:24</t>
         </is>
       </c>
     </row>
@@ -1119,7 +3190,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1000.8</v>
+        <v>996.58</v>
       </c>
     </row>
     <row r="6">
@@ -1129,7 +3200,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1000.8</v>
+        <v>996.58</v>
       </c>
     </row>
     <row r="7">
@@ -1139,7 +3210,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="8">
@@ -1159,7 +3230,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-0.421</v>
       </c>
     </row>
     <row r="10">
@@ -1169,7 +3240,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1179,7 +3250,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1188,6 +3259,9 @@
           <t>win_rate</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>0.333</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1196,7 +3270,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="14">
@@ -1226,7 +3300,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
